--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/qwen_qwen3.8-max_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/qwen_qwen3.8-max_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
@@ -2051,33 +2051,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11651.34041704005</v>
+        <v>11132.66612502048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02345896791666746</v>
+        <v>1977.679207979236</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2116,33 +2118,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>12640.67083300324</v>
+        <v>9502.873249992263</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03704102709889412</v>
+        <v>1088.334375002887</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2181,33 +2185,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.00500003807246685</v>
+        <v>15028.50374998525</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03062502946704626</v>
+        <v>1143.117291969247</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2246,33 +2252,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>12912.26675000507</v>
+        <v>12916.02837498067</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158400068059564</v>
+        <v>2030.841416970361</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2311,33 +2319,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>80101.21362499194</v>
+        <v>11174.88679103553</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1372499973513186</v>
+        <v>1487.716582952999</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2376,33 +2386,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3686.529375030659</v>
+        <v>11165.02595902421</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02795900218188763</v>
+        <v>1460.176124994177</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2441,33 +2453,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.003582972567528486</v>
+        <v>15184.74062503083</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02145796315744519</v>
+        <v>1313.744458951987</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2506,33 +2520,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.004500034265220165</v>
+        <v>13212.76229200885</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02158299321308732</v>
+        <v>1078.657040954567</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2571,33 +2587,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>86434.61933400249</v>
+        <v>12296.33991699666</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01429097028449178</v>
+        <v>1149.600500008091</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2654,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>14553.02383296657</v>
+        <v>7823.688499978743</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03087497316300869</v>
+        <v>1333.568792033475</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2701,33 +2721,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>6978.227375017013</v>
+        <v>14385.20633301232</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03058399306610227</v>
+        <v>1860.879833984654</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2766,33 +2788,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.002124987076967955</v>
+        <v>13084.57970799645</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01312501262873411</v>
+        <v>1298.3405420091</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2831,33 +2855,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>84049.60750002647</v>
+        <v>11620.00383302802</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03691698657348752</v>
+        <v>1513.565666973591</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2896,33 +2922,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>8292.636749974918</v>
+        <v>12682.86895897472</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01641700509935617</v>
+        <v>1523.103874991648</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2961,33 +2989,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>6344.249374989886</v>
+        <v>10635.18016599119</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03908301005139947</v>
+        <v>1509.143292030785</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3026,33 +3056,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.003875000402331352</v>
+        <v>12349.55595899373</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01712498487904668</v>
+        <v>1684.502416988835</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3091,33 +3123,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.003999972250312567</v>
+        <v>10148.1354580028</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02008397132158279</v>
+        <v>1619.169041048735</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
